--- a/capstone/sprint2/26-09-sprint-2-initial-metrics.xlsx
+++ b/capstone/sprint2/26-09-sprint-2-initial-metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowan\SoftwareEngineering\capstone\Stone-Ocean-Backlogs\capstone\sprint2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268009B2-7421-483D-8E9D-D6B0B7A74E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25D7910-6210-4B29-B976-6CBC95CD70DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -167,6 +167,12 @@
   </si>
   <si>
     <t>Sep 11 2026</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>Sep 11 2026; 9:07 PM</t>
   </si>
 </sst>
 </file>
@@ -533,7 +539,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26F2F5C-9428-EA43-9432-B11B4A37F6BD}">
   <dimension ref="A1:I1003"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -541,7 +547,7 @@
     <col min="7" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -11666,7 +11672,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -17989,7 +17995,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AC37C3-57FD-E44A-8B5F-68D0EAC49E65}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -17998,7 +18004,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -24335,7 +24341,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22623D9-D265-E341-9D40-D4F8180816A9}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -24344,7 +24350,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -30681,7 +30687,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE28E1FE-DF56-8B47-AF8A-1EC59E1B4672}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -30690,7 +30696,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37027,7 +37033,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14211EDA-4B61-5345-86E3-D319343FC73C}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -37036,7 +37042,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37352,9 +37358,13 @@
       <c r="A21" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="10"/>
+      <c r="B21" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
+      <c r="D21" s="17" t="s">
+        <v>43</v>
+      </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
